--- a/Anusreemv2004_filtered_repos.xlsx
+++ b/Anusreemv2004_filtered_repos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,6 +435,26 @@
       <c r="D1" t="inlineStr">
         <is>
           <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>scan_repo</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>https://github.com/Anusreemv2004/scan_repo</t>
+        </is>
+      </c>
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>changes required</t>
         </is>
       </c>
     </row>

--- a/Anusreemv2004_filtered_repos.xlsx
+++ b/Anusreemv2004_filtered_repos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,32 +429,17 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Sensitivity</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
-          <t>scan_repo</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>https://github.com/Anusreemv2004/scan_repo</t>
-        </is>
-      </c>
-      <c r="C2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>changes required</t>
+          <t>Contains_pi</t>
         </is>
       </c>
     </row>
